--- a/content/Question Bank/MCQ/Unit 3 - Control Flow/Unit 3 - Control Flow - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 3 - Control Flow/Unit 3 - Control Flow - MCQ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Python - MCQ - 3.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Python - MCQ - 3.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Python - MCQ - 3.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Python - MCQ - 3.4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 3.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 3.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 3.3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 3.4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,26 +643,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Because printing any value to the screen always requires some condition to be explicitly checked first</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Because it executes the same fixed sequence of steps regardless of the input's value, with no choice between actions</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Because printing any value to the screen always requires a condition to be checked first</t>
-        </is>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>Because any program that accepts input from a user always requires control flow</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Because the act of doubling a number is itself considered a decision-making operation</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Because any program that accepts input from a user always requires control flow</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -721,17 +721,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>'Pass', because achieving a Distinction requires a score of exactly 75</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>'Pass', because the loosest condition is checked first and matches before the stricter one is ever reached</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>'Distinction', because Python checks the more specific condition first automatically</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>'Pass', because achieving a Distinction requires a score of exactly 75</t>
+          <t>'Distinction', because Python always checks the more specific condition first, automatically and silently</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -799,26 +799,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Checking in ascending order simply runs measurably faster overall</t>
+          <t>Python syntactically requires all conditions to be in descending numeric order</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>The order of conditions never actually matters at all in an elif chain</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>Checking from highest to lowest ensures a high score isn't wrongly caught by a lower threshold first</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>The order of conditions never actually matters at all in an elif chain</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Python syntactically requires all conditions to be in descending numeric order</t>
+          <t>Checking in ascending order simply runs measurably faster overall on every machine and dataset</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -955,26 +955,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Runs before the if block</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Runs only when the if condition is `False`</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>Runs only when the if condition is `True`</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Always runs, regardless of the condition</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Runs before the if block</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Runs only when the if condition is `False`</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>It only ever works correctly inside loops, not regular functions</t>
+          <t>It keeps the main logic flat at one indentation level instead of nested several levels deep</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1043,16 +1043,16 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>It keeps the main logic flat at one indentation level instead of nested several levels deep</t>
+          <t>It completely removes the need for writing any condition at all</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>It completely removes the need for writing any condition at all</t>
+          <t>It only ever works correctly inside loops, never inside regular standalone functions</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1121,16 +1121,16 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>'Stop'</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>A full statement that cannot be assigned to a variable</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>A standalone function definition with a name</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>A full statement that cannot be assigned to a variable</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1267,26 +1267,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>"no" (a non-empty string)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>`None` (always falsy)</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>"" (an empty string is falsy)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>"no" (a non-empty string)</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>`None` (always falsy)</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>0 (the number zero, falsy)</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1345,26 +1345,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>`.upper()`</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>`.isalpha()`</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>`.strip()`</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>`.isdigit()`</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>`.upper()`</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>`.isalpha()`</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1529,17 +1529,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>Welcome admin</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Please log in</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Nothing</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Please log in</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Welcome admin</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1602,26 +1602,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>if condition: value_true else value_false</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>value_true else condition if value_false</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>value_true if condition else value_false</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>condition ? value_true : value_false</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>if condition: value_true else value_false</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>value_true else condition if value_false</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1680,26 +1680,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Both lines print one after the other, since score is less than 40</t>
+          <t>Nothing at all gets printed to the screen in this case</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>Only 'Result recorded' prints, since it sits outside the if block and always runs</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>Only the word 'Pass' gets printed, and nothing else runs</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Nothing at all gets printed to the screen in this case</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Only 'Result recorded' prints, since it sits outside the if block and always runs</t>
+          <t>Both lines print one after the other in sequence, since score is less than 40</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1758,26 +1758,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>if (x &gt; 5) then:</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>if x &gt; 5:</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>if x &gt; 5 then</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>when x &gt; 5:</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>if x &gt; 5 then</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>if (x &gt; 5) then:</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>if x &gt; 5:</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1836,26 +1836,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>Invalid</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1919,21 +1919,21 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>Printing the word 'Hello' to the screen just once</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Adding two fixed numbers together and printing the result</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>Checking a user's age before allowing entry to a website</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Printing the word 'Hello' to the screen just once</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Adding two fixed numbers together and printing the result</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1997,21 +1997,21 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Python does not technically allow two completely separate if statements written this way at all</t>
+          <t>There is no risk at all here, since they behave in every way completely identically to a single if-else</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>Python does not technically allow two completely separate if statements written this way at all in any script, ever</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>If the conditions are later edited inconsistently, both or neither might run, since the two ifs are evaluated independently</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>There is no risk at all here, since they behave in every way completely identically to a single if-else</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2148,26 +2148,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>Low balance</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>The number 300 is printed as-is</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Nothing at all gets printed here</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>An error is raised instead</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Low balance</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>Completely replace the need for an else block</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>Define a brand new function from scratch</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Completely replace the need for an else block</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2405,26 +2405,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>if `name == True`:</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>if not name:</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>if name:</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>if `name == True`:</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>if `len(name)`:</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -2483,26 +2483,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>`True` or `False`</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>A plain text string value</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>A list of several values</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>A single numeric value</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>`True` or `False`</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Nothing</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Both</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -2639,26 +2639,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Combining two separate conditions together into one using the and operator</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Writing a single if statement that intentionally has no else clause attached to it anywhere at all</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>Placing one if statement inside the body of another, so the inner one is only checked if the outer one is `True`</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Running two completely unrelated if statements one after another, side by side</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Writing a single if statement that intentionally has no else clause attached to it</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Combining two separate conditions together into one using the and operator</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2717,14 +2717,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Python does not technically allow grade to be used as a variable name in match/case</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>match/case matches fixed patterns, not open-ended ranges, so range checks still need if/elif</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Python does not technically allow grade to be used as a variable name</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>match/case simply cannot be used with numeric values at all</t>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2795,26 +2795,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>`True`</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>'minor'</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'adult'</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>`False`</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>'adult'</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>`True`</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2873,26 +2873,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>It is just a style preference with no real effect</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>It simply makes the code execute faster</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>It is only required for very long code blocks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>It simply makes the code execute faster</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Indentation defines which statements belong to the if block</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>It is just a style preference with no real effect</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2951,26 +2951,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Can only ever be used when comparing numeric values</t>
+          <t>Stops checking further conditions once one branch has matched and run</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Stops checking further conditions once one branch has matched and run</t>
+          <t>Runs every single matching block it happens to find</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Runs every single matching block it happens to find</t>
+          <t>Requires no condition to be written at all, ever</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Requires no condition to be written at all, ever</t>
+          <t>Can only ever be used when comparing purely numeric values directly</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3029,26 +3029,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>0 is falsy, so the check cannot distinguish 'no discount set' from 'a real discount of 0', which is likely the wrong check here</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>The code contains an actual syntax error that stops the entire program from running</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>The variable discount must first be explicitly converted into a string for this check to work correctly</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0 is falsy, so the check cannot distinguish 'no discount set' from 'a real discount of 0', which is likely the wrong check here</t>
+          <t>This is considered a genuine bug in Python itself, and zero really should be treated as truthy</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>This is considered a genuine bug in Python itself, and zero really should be treated as truthy</t>
+          <t>The variable discount must first be explicitly converted into a string before this particular check can work correctly at all</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3107,26 +3107,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>[1, 2, 3]</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>"hello"</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3286,26 +3286,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Out of range</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Not a number</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>It would crash immediately the very moment the program runs</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>It would ask the user to manually choose the correct rate every single time</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>It would somehow manage to correctly apply both shipping rates to the order at once</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>It would crash immediately the very moment the program runs</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>It would ask the user to manually choose the correct rate every single time</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -3442,26 +3442,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>Always both</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>It depends on indentation</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>Neither, ever</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Always both</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Exactly one, never both</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>It depends on indentation</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3520,17 +3520,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Indentation rules simply do not apply to nested if statements at all</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>The exact same indentation as the outer if statement</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>It must always be written on a single line of code</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>The exact same indentation as the outer if statement</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Indentation rules simply do not apply to nested if statements at all</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -3603,17 +3603,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>Defining an entirely new custom variable type</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Comparing one value against several fixed possible options</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>Repeating the exact same block of code</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Comparing one value against several fixed possible options</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Defining an entirely new custom variable type</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Ternary expressions technically cannot use any elif-style branching logic internally at all</t>
+          <t>It becomes hard to read, since ternary expressions are meant for simple two-way choices, not several chained branches</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -3686,16 +3686,16 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>It becomes hard to read, since ternary expressions are meant for simple two-way choices, not several chained branches</t>
+          <t>It will immediately raise a `SyntaxError` the moment the program is run</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>It will immediately raise a `SyntaxError` the moment the program is run</t>
+          <t>Ternary expressions technically cannot use any elif-style branching logic internally at all, ever, by design</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3759,21 +3759,21 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>The indented block is skipped entirely</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Python pauses execution and asks the user for new input</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>The entire program crashes immediately as a result</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Python pauses execution and asks the user for new input</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>The indented block is skipped entirely</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -3832,26 +3832,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>Items found here</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Error occurs</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>Cart is empty</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Error occurs</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Nothing at all</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Items found here</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -3910,26 +3910,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>It safely prints 'Not a number' first, avoiding any crash entirely, as intended</t>
+          <t>It safely prints 'Not a number' first, avoiding any crash entirely, exactly as originally intended here</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>It crashes with a `ValueError`, because the conversion is attempted before checking the text is actually numeric</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>It prints 'Out of range' as the result without any error occurring at all</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>It simply prints 'Accepted' as the final result without any issue occurring</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>It prints 'Out of range' as the result without any error occurring at all</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>It crashes with a `ValueError`, because the conversion is attempted before checking the text is actually numeric</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -3988,14 +3988,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>Because users can type unexpected or incorrectly formatted values that would otherwise break the program's logic</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>Because validating input somehow makes programs run measurably faster overall</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Because the Python language technically requires input validation by law</t>
-        </is>
-      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>Because the `input()` function itself is always fundamentally broken and unreliable</t>
@@ -4003,11 +4003,11 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Because users can type unexpected or incorrectly formatted values that would otherwise break the program's logic</t>
+          <t>Because the Python language technically requires input validation by law in every single script, always</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/content/Question Bank/MCQ/Unit 3 - Control Flow/Unit 3 - Control Flow - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 3 - Control Flow/Unit 3 - Control Flow - MCQ.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A guard clause like if not logged_in: return early in a function lets the rest of the function avoid nesting all its logic inside if logged_in:. Why is this generally easier to read?</t>
+          <t>A guard clause like if not `logged_in`: return early in a function lets the rest of the function avoid nesting all its logic inside if `logged_in`:. Why is this generally easier to read?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>`logged_in = True`, `is_admin = False`. if logged_in: if is_admin: `print('Welcome admin')` else: `print('Welcome user')` else: `print('Please log in')`. What prints?</t>
+          <t>`logged_in = True`, `is_admin = False`. if `logged_in`: if `is_admin`: `print('Welcome admin')` else: `print('Welcome user')` else: `print('Please log in')`. What prints?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>logged_in is `True` so we enter the outer block; is_admin is `False` so the inner else runs, printing Welcome user.</t>
+          <t>`logged_in` is `True` so we enter the outer block; `is_admin` is `False` so the inner else runs, printing Welcome user.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Python's ternary form reads value_if_true if condition else value_if_false.</t>
+          <t>Python's ternary form reads `value_if_true` if condition else `value_if_false`.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1602,22 +1602,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>if condition: value_true else value_false</t>
+          <t>if condition: `value_true` else `value_false`</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>value_true else condition if value_false</t>
+          <t>`value_true` else condition if `value_false`</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>value_true if condition else value_false</t>
+          <t>`value_true` if condition else `value_false`</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>condition ? value_true : value_false</t>
+          <t>condition ? `value_true` : `value_false`</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>`int(age_text)` is evaluated first, before checking whether age_text is even a number; converting 'abc' immediately raises a `ValueError` and crashes the program, because the digit check should always run before attempting the conversion, not after.</t>
+          <t>`int(age_text)` is evaluated first, before checking whether `age_text` is even a number; converting 'abc' immediately raises a `ValueError` and crashes the program, because the digit check should always run before attempting the conversion, not after.</t>
         </is>
       </c>
       <c r="D10" t="n">

--- a/content/Question Bank/MCQ/Unit 3 - Control Flow/Unit 3 - Control Flow - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 3 - Control Flow/Unit 3 - Control Flow - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - Unit 3" sheetId="1" r:id="R03e5cc6f6658411f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - Unit 3" sheetId="1" r:id="Re71a642669404d1d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,12 +26,27 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -45,7 +60,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -57,6 +72,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -394,55 +418,55 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="8" t="str">
         <x:v>title</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="8" t="str">
         <x:v>description</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="8" t="str">
         <x:v>explanation</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="8" t="str">
         <x:v>score</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="8" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="F1" s="3" t="str">
+      <x:c r="F1" s="8" t="str">
         <x:v>difficulty</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="str">
+      <x:c r="G1" s="8" t="str">
         <x:v>bloomTaxonomy</x:v>
       </x:c>
-      <x:c r="H1" s="3" t="str">
+      <x:c r="H1" s="8" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="I1" s="3" t="str">
+      <x:c r="I1" s="8" t="str">
         <x:v>subjects</x:v>
       </x:c>
-      <x:c r="J1" s="3" t="str">
+      <x:c r="J1" s="8" t="str">
         <x:v>topics</x:v>
       </x:c>
-      <x:c r="K1" s="3" t="str">
+      <x:c r="K1" s="8" t="str">
         <x:v>subTopics</x:v>
       </x:c>
-      <x:c r="L1" s="3" t="str">
+      <x:c r="L1" s="8" t="str">
         <x:v>companies</x:v>
       </x:c>
-      <x:c r="M1" s="3" t="str">
+      <x:c r="M1" s="8" t="str">
         <x:v>option1</x:v>
       </x:c>
-      <x:c r="N1" s="3" t="str">
+      <x:c r="N1" s="8" t="str">
         <x:v>option2</x:v>
       </x:c>
-      <x:c r="O1" s="3" t="str">
+      <x:c r="O1" s="8" t="str">
         <x:v>option3</x:v>
       </x:c>
-      <x:c r="P1" s="3" t="str">
+      <x:c r="P1" s="8" t="str">
         <x:v>option4</x:v>
       </x:c>
-      <x:c r="Q1" s="3" t="str">
+      <x:c r="Q1" s="8" t="str">
         <x:v>answer</x:v>
       </x:c>
     </x:row>
@@ -468,7 +492,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F2" s="4" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G2" s="4" t="str">
         <x:v>analyze</x:v>
@@ -570,7 +594,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F4" s="4" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G4" s="4" t="str">
         <x:v>analyze</x:v>
@@ -626,7 +650,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F5" s="4" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G5" s="4" t="str">
         <x:v>apply</x:v>
@@ -728,7 +752,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F7" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
         <x:v>evaluate</x:v>
@@ -779,7 +803,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F8" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
         <x:v>apply</x:v>
@@ -830,7 +854,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F9" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
         <x:v>apply</x:v>
@@ -881,7 +905,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F10" s="4" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
         <x:v>analyze</x:v>
@@ -932,7 +956,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F11" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
         <x:v>apply</x:v>
@@ -1039,7 +1063,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F13" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
         <x:v>apply</x:v>
@@ -1090,7 +1114,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F14" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
         <x:v>evaluate</x:v>
@@ -1192,7 +1216,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F16" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
         <x:v>analyze</x:v>
@@ -1345,7 +1369,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
         <x:v>analyze</x:v>
@@ -1447,7 +1471,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F21" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
         <x:v>evaluate</x:v>
@@ -1498,7 +1522,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F22" s="4" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
         <x:v>apply</x:v>
@@ -1600,7 +1624,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F24" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
         <x:v>evaluate</x:v>
@@ -1702,7 +1726,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F26" s="4" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
         <x:v>analyze</x:v>
@@ -1804,7 +1828,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F28" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
         <x:v>evaluate</x:v>
@@ -1957,7 +1981,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F31" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
         <x:v>evaluate</x:v>
@@ -2008,7 +2032,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F32" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
         <x:v>apply</x:v>
@@ -2059,7 +2083,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F33" s="4" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G33" s="4" t="str">
         <x:v>analyze</x:v>
@@ -2110,7 +2134,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F34" s="4" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G34" s="4" t="str">
         <x:v>analyze</x:v>
@@ -2161,7 +2185,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F35" s="4" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G35" s="4" t="str">
         <x:v>apply</x:v>
@@ -2212,7 +2236,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F36" s="4" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G36" s="4" t="str">
         <x:v>analyze</x:v>
@@ -2314,7 +2338,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F38" s="4" t="str">
-        <x:v>easy</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G38" s="4" t="str">
         <x:v>evaluate</x:v>
@@ -2416,7 +2440,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F40" s="4" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G40" s="4" t="str">
         <x:v>analyze</x:v>
@@ -2467,7 +2491,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F41" s="4" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G41" s="4" t="str">
         <x:v>apply</x:v>
@@ -2504,7 +2528,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f22949dc2014338"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36e95f41df034c31"/>
   </x:tableParts>
 </x:worksheet>
 </file>